--- a/Project requirement.xlsx
+++ b/Project requirement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\242\Thiết kế hệ thống nhúng\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\242\Thiết kế hệ thống nhúng\BTL TKHTN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78E6AE0-21F9-43D8-A659-3CDBD9F84B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59C0974-197E-499D-B77C-AC17704A118F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D4C57B67-2AF7-4966-A9F3-A6A413F4F807}"/>
   </bookViews>
@@ -25,57 +25,72 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>Yêu cầu cho dự án: Hệ thống quan trắc thời tiết</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Mục tiêu hệ thống </t>
-  </si>
-  <si>
-    <t>Hệ thống quan trắc thời tiết nhằm thu thập, xử lý, lưu trữ và cung cấp thông tin thời tiết theo thời gian thực, hỗ trợ dự báo khí hậu, cảnh báo thiên tai và phục vụ nhu cầu nghiên cứu, sản xuất, đời sống.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Thành phần hệ thống </t>
-  </si>
-  <si>
-    <t>a. Thiết bị cảm biến và trạm đo lường</t>
-  </si>
-  <si>
-    <t>Đo nhiệt độ, độ ẩm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đo tốc độ gió, lượng mưa </t>
-  </si>
-  <si>
-    <t>b. Hệ thống truyền dữ liệu</t>
-  </si>
-  <si>
-    <t>Gửi dữ liệu theo thời gian thực qua mạng không dây ( Lora)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đảm bảo độ tin cậy và tính liên tục trong truyền tải </t>
-  </si>
-  <si>
-    <t>c. Giao diện người dùng</t>
-  </si>
-  <si>
-    <t>Website hiển thị thông tin thời tiết theo thời gian thực</t>
-  </si>
-  <si>
-    <t>3. Yêu cầu chức năng</t>
-  </si>
-  <si>
-    <t>Thu thập dữ liệu từ trạm quan trác</t>
-  </si>
-  <si>
-    <t>Lưu dữ liệu vào thời gian thực</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hiển thị dữ liệu trên web </t>
-  </si>
-  <si>
-    <t>Block diagram</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>1. Tên: Hệ thống quan trắc thời tiết</t>
+  </si>
+  <si>
+    <t>2. Mục đich: Hệ thống quan trắc thời tiết nhằm thu thập, xử lý, lưu trữ và cung cấp thông tin thời tiết theo thời gian thực, hỗ trợ dự báo khí hậu, cảnh báo thiên tai và phục vụ nhu cầu nghiên cứu, sản xuất, đời sống.</t>
+  </si>
+  <si>
+    <t>3. Ngõ vào/ra</t>
+  </si>
+  <si>
+    <t>Ngõ vào: cảm biến nhiệt độ, độ ẩm, cảm biến đo tốc độ gió, lượng mưa</t>
+  </si>
+  <si>
+    <t>Ngõ ra: màn hình LCD, website hiển thị thông tin thời tiết theo thời gian thực</t>
+  </si>
+  <si>
+    <t>4. Trường hợp sử dụng</t>
+  </si>
+  <si>
+    <t>Hệ thống thu thập dữ liệu thời tiết theo chu kỳ và gửi về máy chủ thông qua module GPRS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dữ liệu thời tiết được hiển thị trên màn hình LCD và website hiển thị </t>
+  </si>
+  <si>
+    <t>5. Chức năng</t>
+  </si>
+  <si>
+    <t>Thu thập và phân tích các thông số thời tiết: nhiệt độ, độ ẩm, áp suất khí quyển, tốc độ gió, lượng mưa</t>
+  </si>
+  <si>
+    <t>Truyền dữ liệu thời tiết về máy chủ thông qua module</t>
+  </si>
+  <si>
+    <t>6. Hiệu năng</t>
+  </si>
+  <si>
+    <t>Độ chính xác đo lường ±0.5°C đối với nhiệt độ, ±3% đối với độ ẩm, ±1 hPa đối với áp suất khí quyển, ±0.1 m/s đối với tốc độ gió.</t>
+  </si>
+  <si>
+    <t>7. Giá thành sản xuất</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. Cảm biến nhiệt độ và độ ẩm  </t>
+  </si>
+  <si>
+    <t>a. Vi xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d. Cảm biến tốc độ gió </t>
+  </si>
+  <si>
+    <t>c. Cảm biến lượng mưa</t>
+  </si>
+  <si>
+    <t>e. Màn hình hiển thị LCD</t>
+  </si>
+  <si>
+    <t>8. Công suất (Power): Công suất tiêu thụ 15W cho bộ điều khiển, sử dụng nguồn DC 5V hoặc năng lượng mặt trời.</t>
+  </si>
+  <si>
+    <t>9.Kích thước / cân nặng (Physical size/weight): 10x15x5cm, 500g</t>
+  </si>
+  <si>
+    <t>10. Cài đặt (Installation): Cố định các cảm biến tại vị trí thích hợp để đảm bảo đo lường chính xác. Lắp đặt hệ thống truyền dữ liệu và nguồn điện hoặc tấm pin năng lượng mặt trời đảm bảo hoạt động liên tục.</t>
   </si>
 </sst>
 </file>
@@ -135,55 +150,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>535772</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>122622</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D7F2CEC-EC0B-FDB0-B7FC-BF2AB30B9B8C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="3505200"/>
-          <a:ext cx="16994972" cy="5029902"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -483,100 +449,124 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20EB0CDB-EC3D-4EB8-8A84-3973A89C314F}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C6" s="1" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C7" s="1" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C9" s="1" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C10" s="1" t="s">
+    <row r="10" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
+    <row r="11" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C12" s="1" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>